--- a/CodeSystem-concept-codes.xlsx
+++ b/CodeSystem-concept-codes.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://fhir.org/guides/itech-uw/who-smart-hiv-dak/CodeSystem/concept-codes</t>
+    <t>http://fhir.org/guides/who/hiv-dak/CodeSystem/HIV-DAKConcepts</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>itechuwConceptCodes</t>
+    <t>HIV-DAKConcepts</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>itech-uw Concept Codes</t>
+    <t>HIV-DAK Concepts</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T07:49:07+00:00</t>
+    <t>2024-05-31T12:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Set of codes representing all concepts used in the implementation guide</t>
+    <t>Set of codes representing all concepts used in the HIV-DAK implementation guide</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-concept-codes.xlsx
+++ b/CodeSystem-concept-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T12:57:23+00:00</t>
+    <t>2024-06-06T18:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-concept-codes.xlsx
+++ b/CodeSystem-concept-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T18:19:00+00:00</t>
+    <t>2024-06-06T18:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
